--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/2_Social_Category_Matrix.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/2_Social_Category_Matrix.xlsx
@@ -527,7 +527,7 @@
   <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="101" customWidth="1" min="1" max="1"/>
+    <col width="93" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Distribution of Enterprises Across Business Activities by Social Category (All Rajasthan District)</t>
+          <t>Distribution of Enterprises Across Business Activities by Social Category (Dausa District)</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>1</v>
@@ -651,7 +651,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -674,10 +674,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -699,11 +699,11 @@
       <c r="F7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="8" t="n">
-        <v>1</v>
+      <c r="G7" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -919,10 +919,10 @@
         <v>7</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -987,8 +987,8 @@
           <t>E-mitra</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>1</v>
+      <c r="D18" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -999,8 +999,8 @@
       <c r="G18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
+      <c r="H18" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">

--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/2_Social_Category_Matrix.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/2_Social_Category_Matrix.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>1</v>
@@ -651,7 +651,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -696,14 +696,14 @@
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="8" t="n">
-        <v>1</v>
+      <c r="F7" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>1</v>
+      <c r="H7" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
